--- a/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6614" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6614" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -675,6 +675,10 @@
     <t>Uppmärksamhetsinformation.</t>
   </si>
   <si>
+    <t>getalertinformation3-body-choice:En och endast en av hypersensitivity, activity, condition, decisionNonstandardCareProcedure, informationNonstandardCareProcedure, contagion och unstructuredAlertInformation ska anges {hypersensitivity.combine(activity).combine(condition).combine(decisionNonstandardCareProcedure).combine(informationNonstandardCareProcedure).combine(contagion).combine(unstructuredAlertInformation).count() = 1}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>SEEHDSLMAlertInformationV30.alertInformation.body.id</t>
   </si>
   <si>
@@ -736,6 +740,10 @@
   </si>
   <si>
     <t>Angivelse av den tid då överkänslighet som observerats faktiskt förekom eller förväntas förekomma. Se även regel Verify TimeType.</t>
+  </si>
+  <si>
+    <t>getalertinformation3-time-choice:Ett och endast ett av timestamp och timePeriod ska anges {timestamp.exists() xor timePeriod.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMAlertInformationV30.alertInformation.body.hypersensitivity.time.id</t>
@@ -7210,15 +7218,15 @@
         <v>72</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7315,10 +7323,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7417,10 +7425,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7521,10 +7529,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7550,10 +7558,10 @@
         <v>164</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7604,7 +7612,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -7621,10 +7629,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7650,10 +7658,10 @@
         <v>78</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7704,7 +7712,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7721,10 +7729,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7821,10 +7829,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7923,10 +7931,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8027,10 +8035,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8056,10 +8064,10 @@
         <v>170</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8110,7 +8118,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -8127,10 +8135,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8156,10 +8164,10 @@
         <v>170</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8210,7 +8218,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -8227,10 +8235,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8256,10 +8264,10 @@
         <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8310,7 +8318,7 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -8322,15 +8330,15 @@
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8427,10 +8435,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8529,10 +8537,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8633,10 +8641,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8716,7 +8724,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8733,10 +8741,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8759,13 +8767,13 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8816,7 +8824,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8833,10 +8841,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8862,10 +8870,10 @@
         <v>170</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8916,7 +8924,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -8933,10 +8941,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8962,10 +8970,10 @@
         <v>170</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9016,7 +9024,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -9033,10 +9041,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9062,10 +9070,10 @@
         <v>136</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9116,7 +9124,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -9133,10 +9141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9162,10 +9170,10 @@
         <v>78</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9216,7 +9224,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -9233,10 +9241,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9333,10 +9341,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9435,10 +9443,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9539,10 +9547,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9568,10 +9576,10 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9622,7 +9630,7 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -9639,10 +9647,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9668,10 +9676,10 @@
         <v>170</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9722,7 +9730,7 @@
         <v>72</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -9739,10 +9747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9768,10 +9776,10 @@
         <v>78</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9822,7 +9830,7 @@
         <v>72</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>73</v>
@@ -9834,15 +9842,15 @@
         <v>72</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9939,10 +9947,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10041,10 +10049,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10145,10 +10153,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10228,7 +10236,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>73</v>
@@ -10245,10 +10253,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10271,13 +10279,13 @@
         <v>72</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10328,7 +10336,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10345,10 +10353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10374,10 +10382,10 @@
         <v>78</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10428,7 +10436,7 @@
         <v>72</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -10445,10 +10453,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10545,10 +10553,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10647,10 +10655,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10751,10 +10759,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10780,10 +10788,10 @@
         <v>119</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10834,7 +10842,7 @@
         <v>72</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>73</v>
@@ -10851,10 +10859,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10880,10 +10888,10 @@
         <v>170</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10934,7 +10942,7 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>73</v>
@@ -10951,10 +10959,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10980,10 +10988,10 @@
         <v>170</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11034,7 +11042,7 @@
         <v>72</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>73</v>
@@ -11051,10 +11059,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11080,10 +11088,10 @@
         <v>78</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11134,7 +11142,7 @@
         <v>72</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
@@ -11151,10 +11159,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11251,10 +11259,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11353,10 +11361,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11457,10 +11465,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11486,10 +11494,10 @@
         <v>170</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11540,7 +11548,7 @@
         <v>72</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>
@@ -11557,10 +11565,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11586,10 +11594,10 @@
         <v>164</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11640,7 +11648,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -11657,10 +11665,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11686,10 +11694,10 @@
         <v>78</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11740,7 +11748,7 @@
         <v>72</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -11757,10 +11765,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11857,10 +11865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11959,10 +11967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12063,10 +12071,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12092,10 +12100,10 @@
         <v>170</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12146,7 +12154,7 @@
         <v>72</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -12163,10 +12171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12192,10 +12200,10 @@
         <v>170</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12246,7 +12254,7 @@
         <v>72</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -12263,10 +12271,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12292,10 +12300,10 @@
         <v>78</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12346,7 +12354,7 @@
         <v>72</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
@@ -12358,15 +12366,15 @@
         <v>72</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12463,10 +12471,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12565,10 +12573,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12669,10 +12677,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12752,7 +12760,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -12769,10 +12777,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12795,13 +12803,13 @@
         <v>72</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12852,7 +12860,7 @@
         <v>72</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -12869,10 +12877,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12898,10 +12906,10 @@
         <v>78</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12952,7 +12960,7 @@
         <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12969,10 +12977,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13069,10 +13077,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13171,10 +13179,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13275,10 +13283,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13304,10 +13312,10 @@
         <v>119</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13358,7 +13366,7 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>73</v>
@@ -13375,10 +13383,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13404,10 +13412,10 @@
         <v>170</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13458,7 +13466,7 @@
         <v>72</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>73</v>
@@ -13475,10 +13483,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13504,10 +13512,10 @@
         <v>170</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13558,7 +13566,7 @@
         <v>72</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>73</v>
@@ -13575,10 +13583,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13604,10 +13612,10 @@
         <v>78</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13658,7 +13666,7 @@
         <v>72</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>73</v>
@@ -13675,10 +13683,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13775,10 +13783,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13877,10 +13885,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13981,10 +13989,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14010,10 +14018,10 @@
         <v>170</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14064,7 +14072,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>73</v>
@@ -14081,10 +14089,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14110,10 +14118,10 @@
         <v>164</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14164,7 +14172,7 @@
         <v>72</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -14181,10 +14189,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14210,10 +14218,10 @@
         <v>78</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14264,7 +14272,7 @@
         <v>72</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>73</v>
@@ -14281,10 +14289,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14381,10 +14389,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14483,10 +14491,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14587,10 +14595,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14616,10 +14624,10 @@
         <v>170</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14670,7 +14678,7 @@
         <v>72</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>73</v>
@@ -14687,10 +14695,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14716,10 +14724,10 @@
         <v>170</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14770,7 +14778,7 @@
         <v>72</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>73</v>
@@ -14787,10 +14795,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14816,10 +14824,10 @@
         <v>170</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14870,7 +14878,7 @@
         <v>72</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>73</v>
@@ -14887,10 +14895,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14916,10 +14924,10 @@
         <v>78</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -14970,7 +14978,7 @@
         <v>72</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>73</v>
@@ -14987,10 +14995,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15087,10 +15095,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15189,10 +15197,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15293,10 +15301,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15322,10 +15330,10 @@
         <v>170</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15376,7 +15384,7 @@
         <v>72</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>83</v>
@@ -15393,10 +15401,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15422,10 +15430,10 @@
         <v>170</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15476,7 +15484,7 @@
         <v>72</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>83</v>
@@ -15493,10 +15501,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15522,10 +15530,10 @@
         <v>78</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -15576,7 +15584,7 @@
         <v>72</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>83</v>
@@ -15588,15 +15596,15 @@
         <v>72</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15693,10 +15701,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15795,10 +15803,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15899,10 +15907,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15982,7 +15990,7 @@
         <v>72</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>73</v>
@@ -15999,10 +16007,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16025,13 +16033,13 @@
         <v>72</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16082,7 +16090,7 @@
         <v>72</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>73</v>
@@ -16099,10 +16107,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16128,10 +16136,10 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16182,7 +16190,7 @@
         <v>72</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>83</v>
@@ -16199,10 +16207,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16228,10 +16236,10 @@
         <v>78</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16282,7 +16290,7 @@
         <v>72</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>73</v>
@@ -16299,10 +16307,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16399,10 +16407,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16501,10 +16509,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16605,10 +16613,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16634,10 +16642,10 @@
         <v>170</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16688,7 +16696,7 @@
         <v>72</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>73</v>
@@ -16705,10 +16713,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16734,10 +16742,10 @@
         <v>170</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -16788,7 +16796,7 @@
         <v>72</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>73</v>
@@ -16805,10 +16813,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16834,10 +16842,10 @@
         <v>170</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16888,7 +16896,7 @@
         <v>72</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>73</v>
@@ -16905,10 +16913,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16934,10 +16942,10 @@
         <v>78</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -16988,7 +16996,7 @@
         <v>72</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>73</v>
@@ -17005,10 +17013,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17105,10 +17113,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17207,10 +17215,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17311,10 +17319,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17340,10 +17348,10 @@
         <v>119</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17394,7 +17402,7 @@
         <v>72</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>73</v>
@@ -17411,10 +17419,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17440,10 +17448,10 @@
         <v>170</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -17494,7 +17502,7 @@
         <v>72</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>73</v>
@@ -17511,10 +17519,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17540,10 +17548,10 @@
         <v>170</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -17594,7 +17602,7 @@
         <v>72</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>73</v>
@@ -17611,10 +17619,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17640,10 +17648,10 @@
         <v>78</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17694,7 +17702,7 @@
         <v>72</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>73</v>
@@ -17711,10 +17719,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17811,10 +17819,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17913,10 +17921,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18017,10 +18025,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18046,10 +18054,10 @@
         <v>170</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18100,7 +18108,7 @@
         <v>72</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>73</v>
@@ -18117,10 +18125,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18146,10 +18154,10 @@
         <v>164</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18200,7 +18208,7 @@
         <v>72</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>83</v>
@@ -18217,10 +18225,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18246,10 +18254,10 @@
         <v>78</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -18300,7 +18308,7 @@
         <v>72</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>73</v>
@@ -18317,10 +18325,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18417,10 +18425,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18519,10 +18527,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18623,10 +18631,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18652,10 +18660,10 @@
         <v>170</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18706,7 +18714,7 @@
         <v>72</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -18723,10 +18731,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18752,10 +18760,10 @@
         <v>164</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18806,7 +18814,7 @@
         <v>72</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>73</v>
@@ -18823,10 +18831,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18852,10 +18860,10 @@
         <v>136</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -18906,7 +18914,7 @@
         <v>72</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -18923,10 +18931,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18952,10 +18960,10 @@
         <v>132</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19006,7 +19014,7 @@
         <v>72</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -19023,10 +19031,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19052,10 +19060,10 @@
         <v>78</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19106,7 +19114,7 @@
         <v>72</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>73</v>
@@ -19123,10 +19131,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19223,10 +19231,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19325,10 +19333,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19429,10 +19437,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19458,10 +19466,10 @@
         <v>170</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -19512,7 +19520,7 @@
         <v>72</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>83</v>
@@ -19529,10 +19537,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19558,10 +19566,10 @@
         <v>170</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -19612,7 +19620,7 @@
         <v>72</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -19629,10 +19637,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19658,10 +19666,10 @@
         <v>78</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -19712,7 +19720,7 @@
         <v>72</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>83</v>
@@ -19724,15 +19732,15 @@
         <v>72</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -19829,10 +19837,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -19931,10 +19939,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20035,10 +20043,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20118,7 +20126,7 @@
         <v>72</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>73</v>
@@ -20135,10 +20143,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20161,13 +20169,13 @@
         <v>72</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20218,7 +20226,7 @@
         <v>72</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>73</v>
@@ -20235,10 +20243,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20264,10 +20272,10 @@
         <v>136</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -20318,7 +20326,7 @@
         <v>72</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -20335,10 +20343,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20364,10 +20372,10 @@
         <v>78</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -20418,7 +20426,7 @@
         <v>72</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>73</v>
@@ -20435,10 +20443,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20535,10 +20543,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20637,10 +20645,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -20741,10 +20749,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -20770,10 +20778,10 @@
         <v>170</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -20824,7 +20832,7 @@
         <v>72</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>83</v>
@@ -20841,10 +20849,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -20870,10 +20878,10 @@
         <v>170</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -20924,7 +20932,7 @@
         <v>72</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>83</v>
@@ -20941,10 +20949,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -20970,10 +20978,10 @@
         <v>78</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21024,7 +21032,7 @@
         <v>72</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>83</v>
@@ -21036,15 +21044,15 @@
         <v>72</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21141,10 +21149,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21243,10 +21251,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21347,10 +21355,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21430,7 +21438,7 @@
         <v>72</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>73</v>
@@ -21447,10 +21455,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21473,13 +21481,13 @@
         <v>72</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -21530,7 +21538,7 @@
         <v>72</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>73</v>
@@ -21547,10 +21555,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21576,10 +21584,10 @@
         <v>136</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -21630,7 +21638,7 @@
         <v>72</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>83</v>
@@ -21647,10 +21655,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -21676,10 +21684,10 @@
         <v>78</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -21730,7 +21738,7 @@
         <v>72</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>73</v>
@@ -21747,10 +21755,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -21847,10 +21855,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -21949,10 +21957,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22053,10 +22061,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22082,10 +22090,10 @@
         <v>164</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -22136,7 +22144,7 @@
         <v>72</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>73</v>
@@ -22153,10 +22161,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22182,10 +22190,10 @@
         <v>164</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -22236,7 +22244,7 @@
         <v>72</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>73</v>
@@ -22253,10 +22261,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22282,10 +22290,10 @@
         <v>78</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -22336,7 +22344,7 @@
         <v>72</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>83</v>
@@ -22353,10 +22361,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22453,10 +22461,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22555,10 +22563,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22659,10 +22667,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -22688,10 +22696,10 @@
         <v>164</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -22742,7 +22750,7 @@
         <v>72</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>83</v>
@@ -22759,10 +22767,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -22788,10 +22796,10 @@
         <v>164</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -22842,7 +22850,7 @@
         <v>72</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
+++ b/StructureDefinition-SEEHDSLMAlertInformationV30.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
